--- a/Assets/StreamingAssets/GiftConfigExample.xlsx
+++ b/Assets/StreamingAssets/GiftConfigExample.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="礼物表" sheetId="1" r:id="R5af54d518e70423d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="2" r:id="R84003c588b384ce9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="礼物表" sheetId="1" r:id="R14b6564d460848ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="2" r:id="Rf28ebb156403419b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -400,7 +400,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
-        <x:v>string</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
         <x:v>string</x:v>
@@ -419,8 +419,8 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="15" t="str">
-        <x:v>G_1</x:v>
+      <x:c r="A4" s="16" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="15" t="str">
         <x:v>G-1</x:v>
@@ -439,8 +439,8 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="15" t="str">
-        <x:v>G_2</x:v>
+      <x:c r="A5" s="16" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="15" t="str">
         <x:v>G-2</x:v>
@@ -459,8 +459,8 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="15" t="str">
-        <x:v>G_3</x:v>
+      <x:c r="A6" s="16" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
         <x:v>G-3</x:v>
@@ -479,8 +479,8 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="15" t="str">
-        <x:v>G_4</x:v>
+      <x:c r="A7" s="16" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="15" t="str">
         <x:v>G-4</x:v>
@@ -499,8 +499,8 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="15" t="str">
-        <x:v>G_5</x:v>
+      <x:c r="A8" s="16" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
         <x:v>G-5</x:v>
@@ -581,7 +581,7 @@
         <x:v>ID 写法</x:v>
       </x:c>
       <x:c r="B8" s="23" t="str">
-        <x:v>推荐使用 G_1 / G_2，代码里更统一；Variable 保留旧表 G-1 写法</x:v>
+        <x:v>ID 使用纯数字，例如 1 / 2 / 3；Variable 保留旧表 G-1 写法</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
